--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -63743,13 +63743,13 @@
         <v>4</v>
       </c>
       <c r="S133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T133" t="n">
         <v>4</v>
       </c>
       <c r="U133" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V133" t="n">
         <v>8</v>
@@ -63924,13 +63924,13 @@
         <v>104</v>
       </c>
       <c r="BZ133" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="CA133" t="n">
         <v>1.14</v>
       </c>
       <c r="CB133" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="CC133" t="n">
         <v>0</v>
@@ -64233,10 +64233,10 @@
         <v>13</v>
       </c>
       <c r="Y134" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z134" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
@@ -65172,7 +65172,7 @@
         <v>6</v>
       </c>
       <c r="R136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S136" t="n">
         <v>8</v>
@@ -65184,7 +65184,7 @@
         <v>14</v>
       </c>
       <c r="V136" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W136" t="n">
         <v>12</v>
@@ -65359,10 +65359,10 @@
         <v>1.51</v>
       </c>
       <c r="CA136" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="CB136" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="CC136" t="n">
         <v>0</v>
@@ -65535,42 +65535,42 @@
       </c>
       <c r="ED136" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EE136" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EF136" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EG136" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EH136" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EI136" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EJ136" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EK136" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EL136" t="inlineStr">
@@ -65585,17 +65585,17 @@
       </c>
       <c r="EN136" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EO136" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EP136" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.83</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -68034,13 +68034,13 @@
         <v>10</v>
       </c>
       <c r="T142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U142" t="n">
         <v>18</v>
       </c>
       <c r="V142" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W142" t="n">
         <v>21</v>
@@ -68215,10 +68215,10 @@
         <v>2.18</v>
       </c>
       <c r="CA142" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="CB142" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="CC142" t="n">
         <v>1</v>
@@ -69620,7 +69620,7 @@
         <v>1</v>
       </c>
       <c r="BV145" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BW145" t="n">
         <v>65</v>
@@ -69638,7 +69638,7 @@
         <v>2.09</v>
       </c>
       <c r="CB145" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="CC145" t="n">
         <v>0</v>
@@ -69806,37 +69806,37 @@
       </c>
       <c r="EC145" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="ED145" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EE145" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF145" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EG145" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EH145" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EI145" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EJ145" t="inlineStr"/>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -70032,7 +70032,7 @@
         <v>0</v>
       </c>
       <c r="BF146" t="n">
-        <v>-1</v>
+        <v>30266</v>
       </c>
       <c r="BG146" t="n">
         <v>2</v>
@@ -70988,7 +70988,7 @@
         <v>0</v>
       </c>
       <c r="BF148" t="n">
-        <v>-1</v>
+        <v>18365</v>
       </c>
       <c r="BG148" t="n">
         <v>2</v>
@@ -72144,67 +72144,67 @@
       </c>
       <c r="EA150" t="inlineStr">
         <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EB150" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EB150" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
       <c r="EC150" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="ED150" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EE150" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF150" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EG150" t="inlineStr">
+        <is>
+          <t>10.57</t>
+        </is>
+      </c>
+      <c r="EH150" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="EI150" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EJ150" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EK150" t="inlineStr">
+        <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="EF150" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG150" t="inlineStr">
-        <is>
-          <t>12.01</t>
-        </is>
-      </c>
-      <c r="EH150" t="inlineStr">
-        <is>
-          <t>6.58</t>
-        </is>
-      </c>
-      <c r="EI150" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EJ150" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EK150" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
       <c r="EL150" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EM150" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EN150" t="inlineStr"/>
@@ -72618,80 +72618,64 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="EA151" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EB151" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
+      <c r="EA151" t="inlineStr"/>
+      <c r="EB151" t="inlineStr"/>
       <c r="EC151" t="inlineStr"/>
       <c r="ED151" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EE151" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EF151" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EG151" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EH151" t="inlineStr">
         <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EI151" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EJ151" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EK151" t="inlineStr">
+        <is>
           <t>3.35</t>
         </is>
       </c>
-      <c r="EI151" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EJ151" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EK151" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="EL151" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EM151" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="EL151" t="inlineStr"/>
+      <c r="EM151" t="inlineStr"/>
       <c r="EN151" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EO151" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="EP151" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
@@ -72872,7 +72856,7 @@
         <v>0</v>
       </c>
       <c r="BF152" t="n">
-        <v>-1</v>
+        <v>13772</v>
       </c>
       <c r="BG152" t="n">
         <v>2</v>
@@ -73096,82 +73080,82 @@
       </c>
       <c r="EA152" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EB152" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EC152" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="ED152" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EE152" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF152" t="inlineStr">
+        <is>
           <t>1.92</t>
         </is>
       </c>
-      <c r="EF152" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
       <c r="EG152" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EH152" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EI152" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EJ152" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EK152" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EL152" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EM152" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EN152" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EO152" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EP152" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
@@ -73360,7 +73344,7 @@
         <v>0</v>
       </c>
       <c r="BF153" t="n">
-        <v>-1</v>
+        <v>12602</v>
       </c>
       <c r="BG153" t="n">
         <v>2</v>
@@ -73584,22 +73568,22 @@
       </c>
       <c r="EA153" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EB153" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EC153" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="ED153" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EE153" t="inlineStr">
@@ -73609,7 +73593,7 @@
       </c>
       <c r="EF153" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EG153" t="inlineStr">
@@ -73619,12 +73603,12 @@
       </c>
       <c r="EH153" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EI153" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EJ153" t="inlineStr">
@@ -73634,32 +73618,32 @@
       </c>
       <c r="EK153" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EL153" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EM153" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EN153" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EO153" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EP153" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
@@ -74070,55 +74054,71 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="EA154" t="inlineStr"/>
-      <c r="EB154" t="inlineStr"/>
+      <c r="EA154" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EB154" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="EC154" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="ED154" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EE154" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EF154" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EG154" t="inlineStr">
         <is>
-          <t>16.70</t>
+          <t>16.30</t>
         </is>
       </c>
       <c r="EH154" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="EI154" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EJ154" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EK154" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EL154" t="inlineStr"/>
-      <c r="EM154" t="inlineStr"/>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EL154" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EM154" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
       <c r="EN154" t="inlineStr"/>
       <c r="EO154" t="inlineStr"/>
       <c r="EP154" t="inlineStr"/>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -77116,7 +77116,7 @@
         <v>0</v>
       </c>
       <c r="BF161" t="n">
-        <v>-1</v>
+        <v>27650</v>
       </c>
       <c r="BG161" t="n">
         <v>2</v>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -80448,7 +80448,7 @@
         <v>0</v>
       </c>
       <c r="BF168" t="n">
-        <v>-1</v>
+        <v>23112</v>
       </c>
       <c r="BG168" t="n">
         <v>2</v>
@@ -81388,7 +81388,7 @@
         <v>0</v>
       </c>
       <c r="BF170" t="n">
-        <v>-1</v>
+        <v>15003</v>
       </c>
       <c r="BG170" t="n">
         <v>2</v>
@@ -81876,7 +81876,7 @@
         <v>0</v>
       </c>
       <c r="BF171" t="n">
-        <v>-1</v>
+        <v>28244</v>
       </c>
       <c r="BG171" t="n">
         <v>2</v>
@@ -82364,7 +82364,7 @@
         <v>0</v>
       </c>
       <c r="BF172" t="n">
-        <v>-1</v>
+        <v>38551</v>
       </c>
       <c r="BG172" t="n">
         <v>2</v>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -81904,7 +81904,7 @@
         <v>0</v>
       </c>
       <c r="BF177" t="n">
-        <v>-1</v>
+        <v>56150</v>
       </c>
       <c r="BG177" t="n">
         <v>2</v>
@@ -82018,7 +82018,7 @@
         <v>1</v>
       </c>
       <c r="CR177" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CS177" t="n">
         <v>18</v>
@@ -82352,7 +82352,7 @@
         <v>0</v>
       </c>
       <c r="BF178" t="n">
-        <v>-1</v>
+        <v>23704</v>
       </c>
       <c r="BG178" t="n">
         <v>2</v>
@@ -82804,7 +82804,7 @@
         <v>0</v>
       </c>
       <c r="BF179" t="n">
-        <v>-1</v>
+        <v>18757</v>
       </c>
       <c r="BG179" t="n">
         <v>2</v>
@@ -82852,10 +82852,10 @@
         <v>1</v>
       </c>
       <c r="BV179" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BW179" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BX179" t="n">
         <v>49</v>
@@ -82864,13 +82864,13 @@
         <v>30</v>
       </c>
       <c r="BZ179" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="CA179" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="CB179" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="CC179" t="n">
         <v>0</v>
@@ -83268,7 +83268,7 @@
         <v>0</v>
       </c>
       <c r="BF180" t="n">
-        <v>-1</v>
+        <v>10336</v>
       </c>
       <c r="BG180" t="n">
         <v>2</v>
@@ -83720,7 +83720,7 @@
         <v>0</v>
       </c>
       <c r="BF181" t="n">
-        <v>-1</v>
+        <v>31324</v>
       </c>
       <c r="BG181" t="n">
         <v>-1</v>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -90920,7 +90920,7 @@
         <v>0</v>
       </c>
       <c r="BF197" t="n">
-        <v>-1</v>
+        <v>22931</v>
       </c>
       <c r="BG197" t="n">
         <v>2</v>
@@ -91388,7 +91388,7 @@
         <v>0</v>
       </c>
       <c r="BF198" t="n">
-        <v>-1</v>
+        <v>13720</v>
       </c>
       <c r="BG198" t="n">
         <v>2</v>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -93644,7 +93644,7 @@
         <v>0</v>
       </c>
       <c r="BF203" t="n">
-        <v>-1</v>
+        <v>46841</v>
       </c>
       <c r="BG203" t="n">
         <v>2</v>
@@ -95040,7 +95040,7 @@
         <v>0</v>
       </c>
       <c r="BF206" t="n">
-        <v>-1</v>
+        <v>23341</v>
       </c>
       <c r="BG206" t="n">
         <v>2</v>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -98228,7 +98228,7 @@
         <v>0</v>
       </c>
       <c r="BF213" t="n">
-        <v>-1</v>
+        <v>14879</v>
       </c>
       <c r="BG213" t="n">
         <v>2</v>
@@ -99144,7 +99144,7 @@
         <v>0</v>
       </c>
       <c r="BF215" t="n">
-        <v>-1</v>
+        <v>39161</v>
       </c>
       <c r="BG215" t="n">
         <v>2</v>

--- a/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
+++ b/data/matches/leagues/France_Ligue_1_2025-2026.xlsx
@@ -102652,13 +102652,13 @@
         <v>2</v>
       </c>
       <c r="R223" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S223" t="n">
         <v>12</v>
       </c>
       <c r="T223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U223" t="n">
         <v>14</v>
@@ -102776,7 +102776,7 @@
         <v>0</v>
       </c>
       <c r="BF223" t="n">
-        <v>-1</v>
+        <v>21134</v>
       </c>
       <c r="BG223" t="n">
         <v>2</v>
@@ -102839,10 +102839,10 @@
         <v>1.39</v>
       </c>
       <c r="CA223" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="CB223" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="CC223" t="n">
         <v>0</v>
@@ -103220,7 +103220,7 @@
         <v>0</v>
       </c>
       <c r="BF224" t="n">
-        <v>-1</v>
+        <v>14601</v>
       </c>
       <c r="BG224" t="n">
         <v>2</v>
